--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488285_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488285_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4078</v>
+        <v>5.9783</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7134</v>
+        <v>3.7864</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6944</v>
+        <v>2.1919</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0568</v>
+        <v>4.8044</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7729</v>
+        <v>0.3378</v>
       </c>
       <c r="I2" t="n">
-        <v>1.284</v>
+        <v>4.4666</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2072</v>
+        <v>4.8936</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1384</v>
+        <v>0.8803</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0688</v>
+        <v>4.0133</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1504</v>
+        <v>-0.0893</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3656</v>
+        <v>-0.5426</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2152</v>
+        <v>0.4533</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R2" t="n">
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6904</v>
+        <v>0.859</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5061</v>
+        <v>0.6165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1843</v>
+        <v>0.2425</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3777</v>
+        <v>0.315</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3777</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0176</v>
+        <v>5.1404</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8503</v>
+        <v>4.3309</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1673</v>
+        <v>0.8096</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8044</v>
+        <v>4.758</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3378</v>
+        <v>-2.063</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4666</v>
+        <v>6.821</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8936</v>
+        <v>4.8914</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8803</v>
+        <v>-0.885</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0133</v>
+        <v>5.7764</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0893</v>
+        <v>-0.1334</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5426</v>
+        <v>-1.178</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4533</v>
+        <v>1.0446</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0382</v>
+        <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1017</v>
+        <v>-0.222</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3196</v>
+        <v>-0.2456</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2178</v>
+        <v>0.0236</v>
       </c>
       <c r="V3" t="n">
-        <v>0.315</v>
+        <v>-0.6926</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0249</v>
+        <v>4.8995</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6339</v>
+        <v>3.1805</v>
       </c>
       <c r="F4" t="n">
-        <v>0.391</v>
+        <v>1.719</v>
       </c>
       <c r="G4" t="n">
-        <v>4.758</v>
+        <v>3.0568</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.063</v>
+        <v>1.7729</v>
       </c>
       <c r="I4" t="n">
-        <v>6.821</v>
+        <v>1.284</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8914</v>
+        <v>3.2072</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.885</v>
+        <v>2.1384</v>
       </c>
       <c r="L4" t="n">
-        <v>5.7764</v>
+        <v>1.0688</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1334</v>
+        <v>-0.1504</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.178</v>
+        <v>-0.3656</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0446</v>
+        <v>0.2152</v>
       </c>
       <c r="P4" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3375</v>
+        <v>0.1822</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9426</v>
+        <v>-0.0267</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.395</v>
+        <v>0.2089</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6926</v>
+        <v>-0.3777</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.3777</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0496</v>
+        <v>4.0114</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1713</v>
+        <v>3.9115</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1217</v>
+        <v>0.0999</v>
       </c>
       <c r="G5" t="n">
         <v>2.934</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6817</v>
+        <v>0.2801</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1007</v>
+        <v>0.6395</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.581</v>
+        <v>-0.3594</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3144</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1679</v>
+        <v>0.7798</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4999</v>
+        <v>0.4179</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.332</v>
+        <v>0.3619</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6659</v>
+        <v>-0.223</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2327</v>
+        <v>-1.2076</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4332</v>
+        <v>0.9846</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7413</v>
+        <v>0.1278</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6998</v>
+        <v>-0.6186</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.3508</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4671</v>
+        <v>-0.589</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3917</v>
+        <v>0.2381</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2503</v>
+        <v>0.3908</v>
       </c>
       <c r="T6" t="n">
-        <v>1.685</v>
+        <v>0.2901</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4347</v>
+        <v>0.1007</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3777</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3777</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>R. FLORENTINO MONTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1162</v>
+        <v>0.2714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8528</v>
+        <v>-0.705</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2634</v>
+        <v>0.9764</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.223</v>
+        <v>-0.1795</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2076</v>
+        <v>0.2414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9846</v>
+        <v>-0.4209</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1278</v>
+        <v>-1.1169</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6186</v>
+        <v>-0.5884</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7465000000000001</v>
+        <v>-0.5284</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3508</v>
+        <v>0.9374</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.589</v>
+        <v>0.8299</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2381</v>
+        <v>0.1076</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7272</v>
+        <v>0.2726</v>
       </c>
       <c r="T7" t="n">
-        <v>0.725</v>
+        <v>0.5972</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0022</v>
+        <v>-0.3246</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3144</v>
+        <v>-0.3777</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. FLORENTINO MONTERO</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5094</v>
+        <v>0.1782</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.27</v>
+        <v>-0.9593</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7794</v>
+        <v>1.1375</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1795</v>
+        <v>-0.9326</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2414</v>
+        <v>-0.6407</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4209</v>
+        <v>-0.2919</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1169</v>
+        <v>-0.344</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5884</v>
+        <v>0.163</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5284</v>
+        <v>-0.5071</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9374</v>
+        <v>-0.5885</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8299</v>
+        <v>-0.8037</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1076</v>
+        <v>0.2152</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.7402</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0321</v>
+        <v>0.4965</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5215</v>
+        <v>0.2437</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3777</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1265</v>
+        <v>0.1514</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3625</v>
+        <v>0.4342</v>
       </c>
       <c r="F9" t="n">
-        <v>1.236</v>
+        <v>-0.2827</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9326</v>
+        <v>0.6659</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6407</v>
+        <v>0.2327</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2919</v>
+        <v>0.4332</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.344</v>
+        <v>0.7413</v>
       </c>
       <c r="K9" t="n">
-        <v>0.163</v>
+        <v>0.6998</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5071</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5885</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8037</v>
+        <v>-0.4671</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2152</v>
+        <v>0.3917</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4355</v>
+        <v>0.2338</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.6193</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3422</v>
+        <v>-0.3855</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6337</v>
+        <v>-0.4882</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5042</v>
+        <v>-1.1125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8704</v>
+        <v>0.6242</v>
       </c>
       <c r="G10" t="n">
         <v>0.8544</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1181</v>
+        <v>0.0274</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5807</v>
+        <v>-0.189</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4626</v>
+        <v>0.2164</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6289</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7227</v>
+        <v>-1.0744</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9793</v>
+        <v>-1.3802</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2566</v>
+        <v>0.3059</v>
       </c>
       <c r="G11" t="n">
         <v>0.4552</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6536</v>
+        <v>-0.0053</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0943</v>
+        <v>-0.4952</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4407</v>
+        <v>0.4899</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2654</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4708</v>
+        <v>-3.6876</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3219</v>
+        <v>-2.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1489</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4809</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1959</v>
+        <v>1.9791</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5084</v>
+        <v>1.0303</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6874</v>
+        <v>0.9488</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8888</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.3397</v>
+        <v>16.1602</v>
       </c>
       <c r="E13" t="n">
-        <v>8.283700000000001</v>
+        <v>9.104399999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>7.055899999999999</v>
+        <v>7.056000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>13.7127</v>
@@ -1444,7 +1444,7 @@
         <v>15.3339</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6669000000000005</v>
+        <v>0.6668999999999996</v>
       </c>
       <c r="L13" t="n">
         <v>14.667</v>
@@ -1468,10 +1468,10 @@
         <v>14.823</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9173</v>
+        <v>4.7379</v>
       </c>
       <c r="T13" t="n">
-        <v>2.512</v>
+        <v>3.3329</v>
       </c>
       <c r="U13" t="n">
         <v>1.405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0889</v>
+        <v>3.9011</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9844</v>
+        <v>3.6907</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1045</v>
+        <v>0.2104</v>
       </c>
       <c r="G14" t="n">
         <v>1.7223</v>
@@ -1546,13 +1546,13 @@
         <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1813</v>
+        <v>-0.0065</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1691</v>
+        <v>-0.1246</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0122</v>
+        <v>0.1181</v>
       </c>
       <c r="V14" t="n">
         <v>1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4341</v>
+        <v>-0.1414</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5739</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.008</v>
+        <v>-0.8133</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9023</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9023</v>
+        <v>-0.6096</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6143</v>
+        <v>-0.5164</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.288</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4354</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4278</v>
+        <v>-2.9175</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9924</v>
+        <v>2.1872</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2034</v>
@@ -1780,13 +1780,13 @@
         <v>0.9264</v>
       </c>
       <c r="S17" t="n">
-        <v>0.677</v>
+        <v>0.3821</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9103</v>
+        <v>0.4206</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2333</v>
+        <v>-0.0386</v>
       </c>
       <c r="V17" t="n">
         <v>0.9439</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1253</v>
+        <v>-0.8092</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7238</v>
+        <v>-1.8767</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4015</v>
+        <v>1.0675</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3054</v>
+        <v>-0.268</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1323</v>
+        <v>2.2725</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4377</v>
+        <v>-2.5404</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0859</v>
+        <v>0.2439</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0859</v>
+        <v>1.4252</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.1813</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3913</v>
+        <v>-0.5118</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0464</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4377</v>
+        <v>-1.3591</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5332</v>
+        <v>-0.356</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7287</v>
+        <v>-0.2676</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1955</v>
+        <v>-0.0883</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5247</v>
+        <v>-1.2384</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4374</v>
+        <v>0.3394</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.962</v>
+        <v>-1.5778</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6882</v>
@@ -1936,13 +1936,13 @@
         <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5956</v>
+        <v>-0.3093</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0386</v>
+        <v>-0.0594</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6342</v>
+        <v>-0.25</v>
       </c>
       <c r="V19" t="n">
         <v>1.5738</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.666</v>
+        <v>-1.4185</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3663</v>
+        <v>-1.1155</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7004</v>
+        <v>-0.303</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.268</v>
+        <v>-0.3054</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2725</v>
+        <v>0.1323</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5404</v>
+        <v>-0.4377</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2439</v>
+        <v>0.0859</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4252</v>
+        <v>0.0859</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1813</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5118</v>
+        <v>-0.3913</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.0464</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3591</v>
+        <v>-0.4377</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1853</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2127</v>
+        <v>0.24</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7573</v>
+        <v>0.337</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4554</v>
+        <v>-0.097</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5436</v>
+        <v>-2.0183</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5058</v>
+        <v>-1.4708</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0378</v>
+        <v>-0.5475</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7596</v>
+        <v>-1.5688</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3128</v>
+        <v>0.878</v>
       </c>
       <c r="I21" t="n">
         <v>-2.4468</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1255</v>
+        <v>-0.1048</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1456</v>
+        <v>1.1595</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0201</v>
+        <v>-1.2643</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8851</v>
+        <v>-1.464</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4584</v>
+        <v>-0.2814</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4267</v>
+        <v>-1.1826</v>
       </c>
       <c r="P21" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1164</v>
+        <v>-0.6348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0373</v>
+        <v>-0.4396</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0791</v>
+        <v>-0.1952</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7848</v>
+        <v>-2.4692</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4919</v>
+        <v>-0.6037</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2929</v>
+        <v>-1.8654</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4197</v>
+        <v>-2.7596</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2344</v>
+        <v>-0.3128</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6542</v>
+        <v>-2.4468</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7964</v>
+        <v>0.1255</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7857</v>
+        <v>0.1456</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0107</v>
+        <v>-0.0201</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2161</v>
+        <v>-2.8851</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5513</v>
+        <v>-0.4584</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6648</v>
+        <v>-2.4267</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0055</v>
+        <v>-0.042</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3619</v>
+        <v>-0.1352</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3673</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.926</v>
+        <v>-2.7608</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6667</v>
+        <v>-0.394</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2593</v>
+        <v>-2.3668</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5688</v>
+        <v>-2.4197</v>
       </c>
       <c r="H23" t="n">
-        <v>0.878</v>
+        <v>0.2344</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4468</v>
+        <v>-2.6542</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1048</v>
+        <v>0.7964</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1595</v>
+        <v>0.7857</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2643</v>
+        <v>0.0107</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.464</v>
+        <v>-3.2161</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2814</v>
+        <v>-0.5513</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1826</v>
+        <v>-2.6648</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5425</v>
+        <v>0.0295</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6354</v>
+        <v>-0.2639</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.907</v>
+        <v>0.2935</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4392</v>
+        <v>-3.1208</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2478</v>
+        <v>-1.954</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1914</v>
+        <v>-1.1668</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1209</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9859</v>
+        <v>-0.6675</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4166</v>
+        <v>-0.1228</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5693</v>
+        <v>-0.5447</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8377</v>
+        <v>-3.8634</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9098</v>
+        <v>-2.7139</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.928</v>
+        <v>-1.1496</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4871</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0413</v>
+        <v>0.0155</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.429</v>
+        <v>-0.2331</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4703</v>
+        <v>0.2487</v>
       </c>
       <c r="V25" t="n">
         <v>1.5727</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.3396</v>
+        <v>-13.3809</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.055899999999999</v>
+        <v>-7.0558</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.2836</v>
+        <v>-6.325100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-13.7128</v>
@@ -2461,7 +2461,7 @@
         <v>5.846299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.2252</v>
+        <v>-4.225199999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-15.334</v>
@@ -2482,13 +2482,13 @@
         <v>10.1906</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.9171</v>
+        <v>-1.9586</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4051</v>
+        <v>-1.405</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.512</v>
+        <v>-0.5535000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>6.9226</v>
